--- a/src/main/java/resources/userdata.xlsx
+++ b/src/main/java/resources/userdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pratibpa\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1544B181-2820-4B74-9E2C-66E3E526F618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7417343E-B553-4927-B6A8-38D968336988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A4467B3C-2512-4DA5-8E97-C3B354207830}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <t>ZARA COAT 3</t>
   </si>
   <si>
-    <t>IPHONE 13  PRO</t>
+    <t>iphone 13 pro</t>
   </si>
 </sst>
 </file>
